--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$112</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -623,11 +623,31 @@
         <v>28</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>8978</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>46296.66398726479</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -638,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
@@ -1540,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
@@ -1564,7 +1584,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
@@ -1588,7 +1608,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
@@ -1612,7 +1632,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
@@ -1636,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
@@ -1660,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
@@ -1684,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
@@ -1708,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
@@ -1732,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
@@ -1756,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
@@ -1780,7 +1800,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
@@ -1804,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="F51" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
@@ -1828,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
@@ -1852,7 +1872,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
@@ -1876,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
@@ -1900,7 +1920,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
@@ -1924,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
@@ -1948,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
@@ -1972,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
@@ -1996,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
@@ -2020,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
@@ -2044,7 +2064,7 @@
         <v>18</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1">
@@ -2068,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1">
@@ -2092,7 +2112,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
@@ -2116,7 +2136,7 @@
         <v>21</v>
       </c>
       <c r="F64" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
@@ -2140,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
@@ -2164,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
@@ -2188,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="F67" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
@@ -2212,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="F68" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1">
@@ -2236,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="F69" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
@@ -2260,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
@@ -2284,7 +2304,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
@@ -2308,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
@@ -2332,7 +2352,7 @@
         <v>11</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
@@ -2356,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
@@ -2380,11 +2400,899 @@
         <v>1</v>
       </c>
       <c r="F75" s="17" t="n">
-        <v>46293.66112145912</v>
+        <v>46293.66112145833</v>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>267</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>473</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>606</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>464</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>718</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>553</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>1775</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="n">
+        <v>376</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="17" t="n">
+        <v>46296.66398726479</v>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>46296.66398726479</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F112"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$149</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -643,11 +643,31 @@
         <v>28</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>9147</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>169</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>46308.69368312639</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -658,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2424,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
@@ -2448,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
@@ -2472,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
@@ -2496,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
@@ -2520,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
@@ -2544,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
@@ -2568,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
@@ -2592,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
@@ -2616,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
@@ -2640,7 +2660,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
@@ -2664,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
@@ -2688,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
@@ -2712,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
@@ -2736,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
@@ -2760,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
@@ -2784,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
@@ -2808,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1">
@@ -2832,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1">
@@ -2856,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1">
@@ -2880,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1">
@@ -2904,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1">
@@ -2928,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1">
@@ -2952,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1">
@@ -2976,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1">
@@ -3000,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1">
@@ -3024,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1">
@@ -3048,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1">
@@ -3072,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="104" ht="42" customHeight="1">
@@ -3096,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1">
@@ -3120,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="106" ht="42" customHeight="1">
@@ -3144,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1">
@@ -3168,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="108" ht="42" customHeight="1">
@@ -3192,7 +3212,7 @@
         <v>5</v>
       </c>
       <c r="F108" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="109" ht="42" customHeight="1">
@@ -3216,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="110" ht="42" customHeight="1">
@@ -3240,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1">
@@ -3264,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1">
@@ -3288,11 +3308,899 @@
         <v>0</v>
       </c>
       <c r="F112" s="17" t="n">
-        <v>46296.66398726479</v>
+        <v>46296.66398726852</v>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C115" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="n">
+        <v>277</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D123" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D125" s="16" t="n">
+        <v>479</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F125" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D127" s="16" t="n">
+        <v>619</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F127" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C133" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C135" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="n">
+        <v>1313</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="F135" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B136" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C137" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D137" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F137" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B138" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="n">
+        <v>1451</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F138" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B139" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C139" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C141" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="n">
+        <v>474</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B142" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="n">
+        <v>722</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C143" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="n">
+        <v>563</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F143" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B144" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F145" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B147" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C147" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="n">
+        <v>389</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F147" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="17" t="n">
+        <v>46308.69368312639</v>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="18" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="17" t="n">
+        <v>46308.69368312639</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F112"/>
+  <autoFilter ref="A1:F149"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$187</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -663,11 +663,31 @@
         <v>28</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>9158</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>46310.61039063385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -678,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3332,7 +3352,7 @@
         <v>2</v>
       </c>
       <c r="F113" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="114" ht="42" customHeight="1">
@@ -3356,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1">
@@ -3380,7 +3400,7 @@
         <v>3</v>
       </c>
       <c r="F115" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1">
@@ -3404,7 +3424,7 @@
         <v>3</v>
       </c>
       <c r="F116" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1">
@@ -3428,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="F117" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1">
@@ -3452,7 +3472,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1">
@@ -3476,7 +3496,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1">
@@ -3500,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
@@ -3524,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="F121" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
@@ -3548,7 +3568,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
@@ -3572,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
@@ -3596,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1">
@@ -3620,7 +3640,7 @@
         <v>6</v>
       </c>
       <c r="F125" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1">
@@ -3644,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="F126" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1">
@@ -3668,7 +3688,7 @@
         <v>13</v>
       </c>
       <c r="F127" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1">
@@ -3692,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1">
@@ -3716,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="F129" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
@@ -3740,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
@@ -3764,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1">
@@ -3788,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1">
@@ -3812,7 +3832,7 @@
         <v>3</v>
       </c>
       <c r="F133" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
@@ -3836,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
@@ -3860,7 +3880,7 @@
         <v>17</v>
       </c>
       <c r="F135" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1">
@@ -3884,7 +3904,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1">
@@ -3908,7 +3928,7 @@
         <v>9</v>
       </c>
       <c r="F137" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1">
@@ -3932,7 +3952,7 @@
         <v>24</v>
       </c>
       <c r="F138" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1">
@@ -3956,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
@@ -3980,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
@@ -4004,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
@@ -4028,7 +4048,7 @@
         <v>4</v>
       </c>
       <c r="F142" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="143" ht="42" customHeight="1">
@@ -4052,7 +4072,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="144" ht="42" customHeight="1">
@@ -4076,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="F144" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="145" ht="42" customHeight="1">
@@ -4100,7 +4120,7 @@
         <v>24</v>
       </c>
       <c r="F145" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1">
@@ -4124,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="147" ht="42" customHeight="1">
@@ -4148,7 +4168,7 @@
         <v>13</v>
       </c>
       <c r="F147" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="148" ht="42" customHeight="1">
@@ -4172,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="F148" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
       </c>
     </row>
     <row r="149" ht="42" customHeight="1">
@@ -4196,11 +4216,921 @@
         <v>1</v>
       </c>
       <c r="F149" s="17" t="n">
-        <v>46308.69368312639</v>
+        <v>46308.693683125</v>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uJ-U7cs_P_0C</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="inlineStr">
+        <is>
+          <t>AD-SRF: Attack-Defense Semantic Reinforcement for Multi-Modal Image Fusion</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="16" t="n"/>
+      <c r="F150" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B151" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C151" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B153" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C153" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B155" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B157" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C157" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C159" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="n">
+        <v>276</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F160" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C161" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D161" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C163" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F164" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="n">
+        <v>618</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F165" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C166" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B167" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C167" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C168" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C171" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B173" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C173" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F173" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B175" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C175" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B176" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C177" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="179" ht="42" customHeight="1">
+      <c r="A179" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D179" s="16" t="n">
+        <v>474</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="180" ht="42" customHeight="1">
+      <c r="A180" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="n">
+        <v>723</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B181" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C181" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D181" s="16" t="n">
+        <v>564</v>
+      </c>
+      <c r="E181" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C182" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="183" ht="42" customHeight="1">
+      <c r="A183" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B183" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C183" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="184" ht="42" customHeight="1">
+      <c r="A184" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="185" ht="42" customHeight="1">
+      <c r="A185" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C185" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="n">
+        <v>389</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="186" ht="42" customHeight="1">
+      <c r="A186" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B186" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="17" t="n">
+        <v>46310.61039063385</v>
+      </c>
+    </row>
+    <row r="187" ht="42" customHeight="1">
+      <c r="A187" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C187" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D187" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="17" t="n">
+        <v>46310.61039063385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F149"/>
+  <autoFilter ref="A1:F187"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$225</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -683,11 +683,31 @@
         <v>28</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>9201</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>46313.61509582514</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -698,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4238,7 +4258,7 @@
       </c>
       <c r="E150" s="16" t="n"/>
       <c r="F150" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="151" ht="42" customHeight="1">
@@ -4262,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="F151" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="152" ht="42" customHeight="1">
@@ -4286,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="153" ht="42" customHeight="1">
@@ -4310,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="F153" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="154" ht="42" customHeight="1">
@@ -4334,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="155" ht="42" customHeight="1">
@@ -4358,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="F155" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="156" ht="42" customHeight="1">
@@ -4382,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="157" ht="42" customHeight="1">
@@ -4406,7 +4426,7 @@
         <v>2</v>
       </c>
       <c r="F157" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="158" ht="42" customHeight="1">
@@ -4430,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="159" ht="42" customHeight="1">
@@ -4454,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="160" ht="42" customHeight="1">
@@ -4478,7 +4498,7 @@
         <v>-1</v>
       </c>
       <c r="F160" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="161" ht="42" customHeight="1">
@@ -4502,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="F161" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="162" ht="42" customHeight="1">
@@ -4526,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="F162" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="163" ht="42" customHeight="1">
@@ -4550,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="164" ht="42" customHeight="1">
@@ -4574,7 +4594,7 @@
         <v>-1</v>
       </c>
       <c r="F164" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="165" ht="42" customHeight="1">
@@ -4598,7 +4618,7 @@
         <v>-1</v>
       </c>
       <c r="F165" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="166" ht="42" customHeight="1">
@@ -4622,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="167" ht="42" customHeight="1">
@@ -4646,7 +4666,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="168" ht="42" customHeight="1">
@@ -4670,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="F168" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="169" ht="42" customHeight="1">
@@ -4694,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="170" ht="42" customHeight="1">
@@ -4718,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="171" ht="42" customHeight="1">
@@ -4742,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="172" ht="42" customHeight="1">
@@ -4766,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="173" ht="42" customHeight="1">
@@ -4790,7 +4810,7 @@
         <v>3</v>
       </c>
       <c r="F173" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="174" ht="42" customHeight="1">
@@ -4814,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="F174" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="175" ht="42" customHeight="1">
@@ -4838,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="176" ht="42" customHeight="1">
@@ -4862,7 +4882,7 @@
         <v>2</v>
       </c>
       <c r="F176" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="177" ht="42" customHeight="1">
@@ -4886,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="178" ht="42" customHeight="1">
@@ -4910,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="F178" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="179" ht="42" customHeight="1">
@@ -4934,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="F179" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="180" ht="42" customHeight="1">
@@ -4958,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="F180" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="181" ht="42" customHeight="1">
@@ -4982,7 +5002,7 @@
         <v>1</v>
       </c>
       <c r="F181" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="182" ht="42" customHeight="1">
@@ -5006,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="183" ht="42" customHeight="1">
@@ -5030,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="F183" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="184" ht="42" customHeight="1">
@@ -5054,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="185" ht="42" customHeight="1">
@@ -5078,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="F185" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="186" ht="42" customHeight="1">
@@ -5102,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="F186" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
       </c>
     </row>
     <row r="187" ht="42" customHeight="1">
@@ -5126,11 +5146,923 @@
         <v>0</v>
       </c>
       <c r="F187" s="17" t="n">
-        <v>46310.61039063385</v>
+        <v>46310.61039063658</v>
+      </c>
+    </row>
+    <row r="188" ht="42" customHeight="1">
+      <c r="A188" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uJ-U7cs_P_0C</t>
+        </is>
+      </c>
+      <c r="C188" s="20" t="inlineStr">
+        <is>
+          <t>AD-SRF: Attack-Defense Semantic Reinforcement for Multi-Modal Image Fusion</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="189" ht="42" customHeight="1">
+      <c r="A189" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B189" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C189" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C190" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="191" ht="42" customHeight="1">
+      <c r="A191" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C191" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D191" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="192" ht="42" customHeight="1">
+      <c r="A192" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B192" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C192" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="193" ht="42" customHeight="1">
+      <c r="A193" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C193" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B194" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C194" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="195" ht="42" customHeight="1">
+      <c r="A195" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C195" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E195" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="196" ht="42" customHeight="1">
+      <c r="A196" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E196" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="197" ht="42" customHeight="1">
+      <c r="A197" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C197" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D197" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C198" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="n">
+        <v>277</v>
+      </c>
+      <c r="E198" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="199" ht="42" customHeight="1">
+      <c r="A199" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C199" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E199" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="200" ht="42" customHeight="1">
+      <c r="A200" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B200" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C200" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D200" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B201" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C201" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="n">
+        <v>481</v>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="202" ht="42" customHeight="1">
+      <c r="A202" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B202" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C202" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D202" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E202" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="203" ht="42" customHeight="1">
+      <c r="A203" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B203" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C203" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D203" s="16" t="n">
+        <v>621</v>
+      </c>
+      <c r="E203" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B204" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C204" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D204" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E204" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B205" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C205" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="E205" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="206" ht="42" customHeight="1">
+      <c r="A206" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B206" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C206" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D206" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="207" ht="42" customHeight="1">
+      <c r="A207" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C207" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="208" ht="42" customHeight="1">
+      <c r="A208" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B208" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C208" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D208" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="209" ht="42" customHeight="1">
+      <c r="A209" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C209" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="210" ht="42" customHeight="1">
+      <c r="A210" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B210" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C210" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="211" ht="42" customHeight="1">
+      <c r="A211" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B211" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C211" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D211" s="16" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E211" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F211" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="212" ht="42" customHeight="1">
+      <c r="A212" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B212" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C212" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E212" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="213" ht="42" customHeight="1">
+      <c r="A213" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B213" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C213" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D213" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E213" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="214" ht="42" customHeight="1">
+      <c r="A214" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B214" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C214" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D214" s="16" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E214" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F214" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="215" ht="42" customHeight="1">
+      <c r="A215" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B215" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C215" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D215" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E215" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="216" ht="42" customHeight="1">
+      <c r="A216" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B216" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C216" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D216" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E216" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="217" ht="42" customHeight="1">
+      <c r="A217" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B217" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C217" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D217" s="16" t="n">
+        <v>475</v>
+      </c>
+      <c r="E217" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="218" ht="42" customHeight="1">
+      <c r="A218" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B218" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C218" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D218" s="16" t="n">
+        <v>723</v>
+      </c>
+      <c r="E218" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="219" ht="42" customHeight="1">
+      <c r="A219" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B219" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C219" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D219" s="16" t="n">
+        <v>566</v>
+      </c>
+      <c r="E219" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F219" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="220" ht="42" customHeight="1">
+      <c r="A220" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B220" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C220" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="221" ht="42" customHeight="1">
+      <c r="A221" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B221" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C221" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D221" s="16" t="n">
+        <v>1808</v>
+      </c>
+      <c r="E221" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F221" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="222" ht="42" customHeight="1">
+      <c r="A222" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B222" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C222" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D222" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E222" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="223" ht="42" customHeight="1">
+      <c r="A223" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B223" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C223" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D223" s="16" t="n">
+        <v>392</v>
+      </c>
+      <c r="E223" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F223" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="224" ht="42" customHeight="1">
+      <c r="A224" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B224" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C224" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D224" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E224" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="17" t="n">
+        <v>46313.61509582514</v>
+      </c>
+    </row>
+    <row r="225" ht="42" customHeight="1">
+      <c r="A225" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B225" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C225" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D225" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E225" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="17" t="n">
+        <v>46313.61509582514</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F187"/>
+  <autoFilter ref="A1:F225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$263</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -703,11 +703,31 @@
         <v>28</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>9221</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>46315.61733719521</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -718,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5170,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="F188" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="189" ht="42" customHeight="1">
@@ -5194,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="F189" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="190" ht="42" customHeight="1">
@@ -5218,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="F190" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="191" ht="42" customHeight="1">
@@ -5242,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="192" ht="42" customHeight="1">
@@ -5266,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="F192" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="193" ht="42" customHeight="1">
@@ -5290,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="F193" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="194" ht="42" customHeight="1">
@@ -5314,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="F194" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="195" ht="42" customHeight="1">
@@ -5338,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="F195" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="196" ht="42" customHeight="1">
@@ -5362,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="F196" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="197" ht="42" customHeight="1">
@@ -5386,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="198" ht="42" customHeight="1">
@@ -5410,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="F198" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="199" ht="42" customHeight="1">
@@ -5434,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="F199" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="200" ht="42" customHeight="1">
@@ -5458,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="201" ht="42" customHeight="1">
@@ -5482,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="F201" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="202" ht="42" customHeight="1">
@@ -5506,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="F202" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="203" ht="42" customHeight="1">
@@ -5530,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="F203" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="204" ht="42" customHeight="1">
@@ -5554,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="F204" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="205" ht="42" customHeight="1">
@@ -5578,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="206" ht="42" customHeight="1">
@@ -5602,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="F206" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="207" ht="42" customHeight="1">
@@ -5626,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="F207" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="208" ht="42" customHeight="1">
@@ -5650,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="F208" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="209" ht="42" customHeight="1">
@@ -5674,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="F209" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="210" ht="42" customHeight="1">
@@ -5698,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="F210" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="211" ht="42" customHeight="1">
@@ -5722,7 +5742,7 @@
         <v>6</v>
       </c>
       <c r="F211" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="212" ht="42" customHeight="1">
@@ -5746,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="F212" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="213" ht="42" customHeight="1">
@@ -5770,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="F213" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="214" ht="42" customHeight="1">
@@ -5794,7 +5814,7 @@
         <v>10</v>
       </c>
       <c r="F214" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="215" ht="42" customHeight="1">
@@ -5818,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="F215" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="216" ht="42" customHeight="1">
@@ -5842,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="F216" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="217" ht="42" customHeight="1">
@@ -5866,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="F217" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="218" ht="42" customHeight="1">
@@ -5890,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="F218" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="219" ht="42" customHeight="1">
@@ -5914,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="F219" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="220" ht="42" customHeight="1">
@@ -5938,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="221" ht="42" customHeight="1">
@@ -5962,7 +5982,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="222" ht="42" customHeight="1">
@@ -5986,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="F222" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="223" ht="42" customHeight="1">
@@ -6010,7 +6030,7 @@
         <v>3</v>
       </c>
       <c r="F223" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="224" ht="42" customHeight="1">
@@ -6034,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="F224" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
       </c>
     </row>
     <row r="225" ht="42" customHeight="1">
@@ -6058,11 +6078,923 @@
         <v>0</v>
       </c>
       <c r="F225" s="17" t="n">
-        <v>46313.61509582514</v>
+        <v>46313.61509582176</v>
+      </c>
+    </row>
+    <row r="226" ht="42" customHeight="1">
+      <c r="A226" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B226" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uJ-U7cs_P_0C</t>
+        </is>
+      </c>
+      <c r="C226" s="20" t="inlineStr">
+        <is>
+          <t>AD-SRF: Attack-Defense Semantic Reinforcement for Multi-Modal Image Fusion</t>
+        </is>
+      </c>
+      <c r="D226" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="227" ht="42" customHeight="1">
+      <c r="A227" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B227" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C227" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E227" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="228" ht="42" customHeight="1">
+      <c r="A228" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B228" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C228" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D228" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E228" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="229" ht="42" customHeight="1">
+      <c r="A229" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B229" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C229" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D229" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="E229" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="230" ht="42" customHeight="1">
+      <c r="A230" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B230" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C230" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D230" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="231" ht="42" customHeight="1">
+      <c r="A231" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B231" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C231" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D231" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E231" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="232" ht="42" customHeight="1">
+      <c r="A232" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B232" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C232" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D232" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E232" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="233" ht="42" customHeight="1">
+      <c r="A233" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B233" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C233" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D233" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E233" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="234" ht="42" customHeight="1">
+      <c r="A234" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B234" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C234" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D234" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E234" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="235" ht="42" customHeight="1">
+      <c r="A235" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B235" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C235" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D235" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="236" ht="42" customHeight="1">
+      <c r="A236" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B236" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C236" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D236" s="16" t="n">
+        <v>277</v>
+      </c>
+      <c r="E236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="237" ht="42" customHeight="1">
+      <c r="A237" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B237" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C237" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E237" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="238" ht="42" customHeight="1">
+      <c r="A238" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B238" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C238" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D238" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="E238" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="239" ht="42" customHeight="1">
+      <c r="A239" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B239" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C239" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="n">
+        <v>484</v>
+      </c>
+      <c r="E239" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F239" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="240" ht="42" customHeight="1">
+      <c r="A240" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B240" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C240" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D240" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E240" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="241" ht="42" customHeight="1">
+      <c r="A241" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B241" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C241" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="n">
+        <v>622</v>
+      </c>
+      <c r="E241" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="242" ht="42" customHeight="1">
+      <c r="A242" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B242" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C242" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D242" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E242" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="243" ht="42" customHeight="1">
+      <c r="A243" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B243" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C243" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="E243" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="244" ht="42" customHeight="1">
+      <c r="A244" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B244" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C244" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D244" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E244" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="245" ht="42" customHeight="1">
+      <c r="A245" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B245" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C245" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="246" ht="42" customHeight="1">
+      <c r="A246" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B246" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C246" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D246" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="247" ht="42" customHeight="1">
+      <c r="A247" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B247" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C247" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E247" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="248" ht="42" customHeight="1">
+      <c r="A248" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B248" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C248" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D248" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="249" ht="42" customHeight="1">
+      <c r="A249" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B249" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C249" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E249" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="250" ht="42" customHeight="1">
+      <c r="A250" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C250" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D250" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E250" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="251" ht="42" customHeight="1">
+      <c r="A251" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B251" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C251" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E251" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="252" ht="42" customHeight="1">
+      <c r="A252" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B252" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C252" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D252" s="16" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E252" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F252" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="253" ht="42" customHeight="1">
+      <c r="A253" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B253" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C253" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D253" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E253" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="254" ht="42" customHeight="1">
+      <c r="A254" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B254" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C254" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D254" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E254" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="255" ht="42" customHeight="1">
+      <c r="A255" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B255" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C255" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D255" s="16" t="n">
+        <v>477</v>
+      </c>
+      <c r="E255" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F255" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="256" ht="42" customHeight="1">
+      <c r="A256" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B256" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C256" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D256" s="16" t="n">
+        <v>724</v>
+      </c>
+      <c r="E256" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="257" ht="42" customHeight="1">
+      <c r="A257" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B257" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C257" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="n">
+        <v>568</v>
+      </c>
+      <c r="E257" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F257" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="258" ht="42" customHeight="1">
+      <c r="A258" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B258" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C258" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="259" ht="42" customHeight="1">
+      <c r="A259" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B259" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D259" s="16" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E259" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F259" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="260" ht="42" customHeight="1">
+      <c r="A260" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B260" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C260" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D260" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E260" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="261" ht="42" customHeight="1">
+      <c r="A261" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B261" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C261" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D261" s="16" t="n">
+        <v>392</v>
+      </c>
+      <c r="E261" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="262" ht="42" customHeight="1">
+      <c r="A262" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B262" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C262" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D262" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E262" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="17" t="n">
+        <v>46315.61733719521</v>
+      </c>
+    </row>
+    <row r="263" ht="42" customHeight="1">
+      <c r="A263" s="18" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B263" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C263" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E263" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="17" t="n">
+        <v>46315.61733719521</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F225"/>
+  <autoFilter ref="A1:F263"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$301</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -723,11 +723,31 @@
         <v>28</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>9236</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>46317.6157046784</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -738,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6102,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="F226" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="227" ht="42" customHeight="1">
@@ -6126,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="F227" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="228" ht="42" customHeight="1">
@@ -6150,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="F228" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="229" ht="42" customHeight="1">
@@ -6174,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F229" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="230" ht="42" customHeight="1">
@@ -6198,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="F230" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="231" ht="42" customHeight="1">
@@ -6222,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="F231" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="232" ht="42" customHeight="1">
@@ -6246,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="F232" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="233" ht="42" customHeight="1">
@@ -6270,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="F233" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="234" ht="42" customHeight="1">
@@ -6294,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="F234" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="235" ht="42" customHeight="1">
@@ -6318,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="F235" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="236" ht="42" customHeight="1">
@@ -6342,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="F236" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="237" ht="42" customHeight="1">
@@ -6366,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="F237" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="238" ht="42" customHeight="1">
@@ -6390,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="F238" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="239" ht="42" customHeight="1">
@@ -6414,7 +6434,7 @@
         <v>3</v>
       </c>
       <c r="F239" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="240" ht="42" customHeight="1">
@@ -6438,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="F240" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="241" ht="42" customHeight="1">
@@ -6462,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="F241" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="242" ht="42" customHeight="1">
@@ -6486,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="F242" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="243" ht="42" customHeight="1">
@@ -6510,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="F243" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="244" ht="42" customHeight="1">
@@ -6534,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="F244" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="245" ht="42" customHeight="1">
@@ -6558,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="F245" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="246" ht="42" customHeight="1">
@@ -6582,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="247" ht="42" customHeight="1">
@@ -6606,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="F247" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="248" ht="42" customHeight="1">
@@ -6630,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="F248" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="249" ht="42" customHeight="1">
@@ -6654,7 +6674,7 @@
         <v>2</v>
       </c>
       <c r="F249" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="250" ht="42" customHeight="1">
@@ -6678,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="F250" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="251" ht="42" customHeight="1">
@@ -6702,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="F251" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="252" ht="42" customHeight="1">
@@ -6726,7 +6746,7 @@
         <v>5</v>
       </c>
       <c r="F252" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="253" ht="42" customHeight="1">
@@ -6750,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="F253" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="254" ht="42" customHeight="1">
@@ -6774,7 +6794,7 @@
         <v>0</v>
       </c>
       <c r="F254" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="255" ht="42" customHeight="1">
@@ -6798,7 +6818,7 @@
         <v>2</v>
       </c>
       <c r="F255" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="256" ht="42" customHeight="1">
@@ -6822,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="F256" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="257" ht="42" customHeight="1">
@@ -6846,7 +6866,7 @@
         <v>2</v>
       </c>
       <c r="F257" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="258" ht="42" customHeight="1">
@@ -6870,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="F258" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="259" ht="42" customHeight="1">
@@ -6894,7 +6914,7 @@
         <v>3</v>
       </c>
       <c r="F259" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="260" ht="42" customHeight="1">
@@ -6918,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="F260" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="261" ht="42" customHeight="1">
@@ -6942,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="F261" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="262" ht="42" customHeight="1">
@@ -6966,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="F262" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
       </c>
     </row>
     <row r="263" ht="42" customHeight="1">
@@ -6990,11 +7010,923 @@
         <v>0</v>
       </c>
       <c r="F263" s="17" t="n">
-        <v>46315.61733719521</v>
+        <v>46315.61733719907</v>
+      </c>
+    </row>
+    <row r="264" ht="42" customHeight="1">
+      <c r="A264" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B264" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uJ-U7cs_P_0C</t>
+        </is>
+      </c>
+      <c r="C264" s="20" t="inlineStr">
+        <is>
+          <t>AD-SRF: Attack-Defense Semantic Reinforcement for Multi-Modal Image Fusion</t>
+        </is>
+      </c>
+      <c r="D264" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="265" ht="42" customHeight="1">
+      <c r="A265" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B265" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C265" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D265" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="266" ht="42" customHeight="1">
+      <c r="A266" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B266" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C266" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D266" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E266" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="267" ht="42" customHeight="1">
+      <c r="A267" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B267" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C267" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D267" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="E267" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B268" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C268" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D268" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E268" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="269" ht="42" customHeight="1">
+      <c r="A269" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B269" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C269" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D269" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E269" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="270" ht="42" customHeight="1">
+      <c r="A270" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B270" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C270" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D270" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E270" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="271" ht="42" customHeight="1">
+      <c r="A271" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B271" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C271" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D271" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E271" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="272" ht="42" customHeight="1">
+      <c r="A272" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B272" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C272" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D272" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E272" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="273" ht="42" customHeight="1">
+      <c r="A273" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B273" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C273" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D273" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E273" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="274" ht="42" customHeight="1">
+      <c r="A274" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B274" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C274" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D274" s="16" t="n">
+        <v>278</v>
+      </c>
+      <c r="E274" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="275" ht="42" customHeight="1">
+      <c r="A275" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B275" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C275" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D275" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E275" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="276" ht="42" customHeight="1">
+      <c r="A276" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B276" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C276" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D276" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E276" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F276" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="277" ht="42" customHeight="1">
+      <c r="A277" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B277" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C277" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D277" s="16" t="n">
+        <v>484</v>
+      </c>
+      <c r="E277" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="278" ht="42" customHeight="1">
+      <c r="A278" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B278" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C278" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D278" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E278" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="279" ht="42" customHeight="1">
+      <c r="A279" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B279" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C279" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D279" s="16" t="n">
+        <v>624</v>
+      </c>
+      <c r="E279" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F279" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="280" ht="42" customHeight="1">
+      <c r="A280" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B280" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C280" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D280" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E280" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="281" ht="42" customHeight="1">
+      <c r="A281" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B281" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C281" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D281" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="E281" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="282" ht="42" customHeight="1">
+      <c r="A282" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B282" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C282" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D282" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E282" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="283" ht="42" customHeight="1">
+      <c r="A283" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B283" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C283" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D283" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="284" ht="42" customHeight="1">
+      <c r="A284" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B284" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C284" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D284" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="285" ht="42" customHeight="1">
+      <c r="A285" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B285" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C285" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D285" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E285" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="286" ht="42" customHeight="1">
+      <c r="A286" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B286" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C286" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D286" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="287" ht="42" customHeight="1">
+      <c r="A287" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B287" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C287" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D287" s="16" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E287" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="288" ht="42" customHeight="1">
+      <c r="A288" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B288" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C288" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D288" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E288" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="289" ht="42" customHeight="1">
+      <c r="A289" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B289" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C289" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D289" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E289" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="290" ht="42" customHeight="1">
+      <c r="A290" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B290" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C290" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D290" s="16" t="n">
+        <v>1471</v>
+      </c>
+      <c r="E290" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F290" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="291" ht="42" customHeight="1">
+      <c r="A291" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B291" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C291" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D291" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E291" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F291" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="292" ht="42" customHeight="1">
+      <c r="A292" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B292" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C292" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D292" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E292" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="293" ht="42" customHeight="1">
+      <c r="A293" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B293" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C293" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D293" s="16" t="n">
+        <v>478</v>
+      </c>
+      <c r="E293" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F293" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="294" ht="42" customHeight="1">
+      <c r="A294" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B294" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C294" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D294" s="16" t="n">
+        <v>725</v>
+      </c>
+      <c r="E294" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F294" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="295" ht="42" customHeight="1">
+      <c r="A295" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B295" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C295" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D295" s="16" t="n">
+        <v>569</v>
+      </c>
+      <c r="E295" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="296" ht="42" customHeight="1">
+      <c r="A296" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B296" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C296" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D296" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="297" ht="42" customHeight="1">
+      <c r="A297" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B297" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C297" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D297" s="16" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E297" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F297" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="298" ht="42" customHeight="1">
+      <c r="A298" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B298" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C298" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D298" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E298" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="299" ht="42" customHeight="1">
+      <c r="A299" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B299" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C299" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D299" s="16" t="n">
+        <v>392</v>
+      </c>
+      <c r="E299" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="300" ht="42" customHeight="1">
+      <c r="A300" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B300" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C300" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D300" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E300" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="17" t="n">
+        <v>46317.6157046784</v>
+      </c>
+    </row>
+    <row r="301" ht="42" customHeight="1">
+      <c r="A301" s="18" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B301" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C301" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E301" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="17" t="n">
+        <v>46317.6157046784</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F263"/>
+  <autoFilter ref="A1:F301"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/data/scholar-citations.xlsx
+++ b/assets/data/scholar-citations.xlsx
@@ -7,8 +7,8 @@
     <sheet name="逐篇论文" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每日引用'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐篇论文'!$A$1:$F$339</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -385,7 +385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -743,11 +743,31 @@
         <v>28</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>9327</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>46322.62367584182</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -758,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7034,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="F264" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="265" ht="42" customHeight="1">
@@ -7058,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="F265" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="266" ht="42" customHeight="1">
@@ -7082,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="F266" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="267" ht="42" customHeight="1">
@@ -7106,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="F267" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="268" ht="42" customHeight="1">
@@ -7130,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="F268" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="269" ht="42" customHeight="1">
@@ -7154,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="F269" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="270" ht="42" customHeight="1">
@@ -7178,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="F270" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="271" ht="42" customHeight="1">
@@ -7202,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="F271" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="272" ht="42" customHeight="1">
@@ -7226,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="F272" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="273" ht="42" customHeight="1">
@@ -7250,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="274" ht="42" customHeight="1">
@@ -7274,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="F274" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="275" ht="42" customHeight="1">
@@ -7298,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="F275" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="276" ht="42" customHeight="1">
@@ -7322,7 +7342,7 @@
         <v>3</v>
       </c>
       <c r="F276" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="277" ht="42" customHeight="1">
@@ -7346,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="F277" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="278" ht="42" customHeight="1">
@@ -7370,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="F278" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="279" ht="42" customHeight="1">
@@ -7394,7 +7414,7 @@
         <v>2</v>
       </c>
       <c r="F279" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="280" ht="42" customHeight="1">
@@ -7418,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="F280" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="281" ht="42" customHeight="1">
@@ -7442,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="F281" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="282" ht="42" customHeight="1">
@@ -7466,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="F282" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="283" ht="42" customHeight="1">
@@ -7490,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="F283" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="284" ht="42" customHeight="1">
@@ -7514,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="F284" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="285" ht="42" customHeight="1">
@@ -7538,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="F285" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="286" ht="42" customHeight="1">
@@ -7562,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="F286" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="287" ht="42" customHeight="1">
@@ -7586,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="F287" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="288" ht="42" customHeight="1">
@@ -7610,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="F288" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="289" ht="42" customHeight="1">
@@ -7634,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="F289" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="290" ht="42" customHeight="1">
@@ -7658,7 +7678,7 @@
         <v>3</v>
       </c>
       <c r="F290" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="291" ht="42" customHeight="1">
@@ -7682,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="F291" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="292" ht="42" customHeight="1">
@@ -7706,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="F292" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="293" ht="42" customHeight="1">
@@ -7730,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="F293" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="294" ht="42" customHeight="1">
@@ -7754,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="F294" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="295" ht="42" customHeight="1">
@@ -7778,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="F295" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="296" ht="42" customHeight="1">
@@ -7802,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="F296" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="297" ht="42" customHeight="1">
@@ -7826,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="F297" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="298" ht="42" customHeight="1">
@@ -7850,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="F298" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="299" ht="42" customHeight="1">
@@ -7874,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="F299" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="300" ht="42" customHeight="1">
@@ -7898,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="F300" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
       </c>
     </row>
     <row r="301" ht="42" customHeight="1">
@@ -7922,11 +7942,923 @@
         <v>0</v>
       </c>
       <c r="F301" s="17" t="n">
-        <v>46317.6157046784</v>
+        <v>46317.61570467593</v>
+      </c>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B302" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uJ-U7cs_P_0C</t>
+        </is>
+      </c>
+      <c r="C302" s="20" t="inlineStr">
+        <is>
+          <t>AD-SRF: Attack-Defense Semantic Reinforcement for Multi-Modal Image Fusion</t>
+        </is>
+      </c>
+      <c r="D302" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="303" ht="42" customHeight="1">
+      <c r="A303" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B303" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:-_dYPAW6P2MC</t>
+        </is>
+      </c>
+      <c r="C303" s="20" t="inlineStr">
+        <is>
+          <t>AnyMatch: Supercharging Universal Multi-modal Image Matching with Large-Scale Single-View Images</t>
+        </is>
+      </c>
+      <c r="D303" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="304" ht="42" customHeight="1">
+      <c r="A304" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B304" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Ybze24A_UAC</t>
+        </is>
+      </c>
+      <c r="C304" s="20" t="inlineStr">
+        <is>
+          <t>ArgMatch: Adaptive Refinement Gathering for Efficient Dense Matching</t>
+        </is>
+      </c>
+      <c r="D304" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E304" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="305" ht="42" customHeight="1">
+      <c r="A305" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B305" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:1yQoGdGgb4wC</t>
+        </is>
+      </c>
+      <c r="C305" s="20" t="inlineStr">
+        <is>
+          <t>C2RF: Bridging Multi-modal Image Registration and Fusion via Commonality Mining and Contrastive Learning</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="E305" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F305" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="306" ht="42" customHeight="1">
+      <c r="A306" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B306" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:WA5NYHcadZ8C</t>
+        </is>
+      </c>
+      <c r="C306" s="20" t="inlineStr">
+        <is>
+          <t>CAMF: An interpretable infrared and visible image fusion network based on class activation mapping</t>
+        </is>
+      </c>
+      <c r="D306" s="16" t="n">
+        <v>111</v>
+      </c>
+      <c r="E306" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="307" ht="42" customHeight="1">
+      <c r="A307" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B307" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:W5xh706n7nkC</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr">
+        <is>
+          <t>CLTE: Infrared and visible image fusion through cross-domain learning and texture-contrast enhancement</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E307" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="308" ht="42" customHeight="1">
+      <c r="A308" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ZuybSZzF8UAC</t>
+        </is>
+      </c>
+      <c r="C308" s="20" t="inlineStr">
+        <is>
+          <t>Comatch: Dynamic covisibility-aware transformer for bilateral subpixel-level semi-dense image matching</t>
+        </is>
+      </c>
+      <c r="D308" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E308" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="309" ht="42" customHeight="1">
+      <c r="A309" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B309" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Fu2w8maKXqMC</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr">
+        <is>
+          <t>Controlfusion: A controllable image fusion network with language-vision degradation prompts</t>
+        </is>
+      </c>
+      <c r="D309" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E309" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="310" ht="42" customHeight="1">
+      <c r="A310" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B310" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:dQ2og3OwTAUC</t>
+        </is>
+      </c>
+      <c r="C310" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning reforms image matching: A survey and outlook</t>
+        </is>
+      </c>
+      <c r="D310" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E310" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="311" ht="42" customHeight="1">
+      <c r="A311" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B311" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:35r97b3x0nAC</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr">
+        <is>
+          <t>Deep learning-based image fusion: A survey</t>
+        </is>
+      </c>
+      <c r="D311" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="E311" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F311" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="312" ht="42" customHeight="1">
+      <c r="A312" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B312" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tkaPQYYpVKoC</t>
+        </is>
+      </c>
+      <c r="C312" s="20" t="inlineStr">
+        <is>
+          <t>Diff-IF: Multi-modality image fusion via diffusion model with fusion knowledge prior</t>
+        </is>
+      </c>
+      <c r="D312" s="16" t="n">
+        <v>283</v>
+      </c>
+      <c r="E312" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F312" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="313" ht="42" customHeight="1">
+      <c r="A313" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B313" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tKAzc9rXhukC</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr">
+        <is>
+          <t>Diff-MEF: Cross-Modal Diffusion Framework With Text Prompts and Semantic Perception for Multi-Exposure Image Fusion</t>
+        </is>
+      </c>
+      <c r="D313" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E313" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="314" ht="42" customHeight="1">
+      <c r="A314" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B314" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:PR6Y55bgFSsC</t>
+        </is>
+      </c>
+      <c r="C314" s="20" t="inlineStr">
+        <is>
+          <t>Diff-Retinex++: Retinex-driven reinforced diffusion model for low-light image enhancement</t>
+        </is>
+      </c>
+      <c r="D314" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E314" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="315" ht="42" customHeight="1">
+      <c r="A315" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B315" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:t6usbXjVLHcC</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>Diff-retinex: Rethinking low-light image enhancement with a generative diffusion model</t>
+        </is>
+      </c>
+      <c r="D315" s="16" t="n">
+        <v>489</v>
+      </c>
+      <c r="E315" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F315" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B316" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JoZmwDi-zQgC</t>
+        </is>
+      </c>
+      <c r="C316" s="20" t="inlineStr">
+        <is>
+          <t>Dispel darkness for better fusion: A controllable visual enhancer based on cross-modal conditional adversarial learning</t>
+        </is>
+      </c>
+      <c r="D316" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="E316" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F316" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="317" ht="42" customHeight="1">
+      <c r="A317" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B317" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:J-pR_7NvFogC</t>
+        </is>
+      </c>
+      <c r="C317" s="20" t="inlineStr">
+        <is>
+          <t>DIVFusion: Darkness-free infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="n">
+        <v>633</v>
+      </c>
+      <c r="E317" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F317" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="318" ht="42" customHeight="1">
+      <c r="A318" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B318" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:q3oQSFYPqjQC</t>
+        </is>
+      </c>
+      <c r="C318" s="20" t="inlineStr">
+        <is>
+          <t>DRLIE: Flexible low-light image enhancement via disentangled representations</t>
+        </is>
+      </c>
+      <c r="D318" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="E318" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="319" ht="42" customHeight="1">
+      <c r="A319" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B319" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:SdhP9T11ey4C</t>
+        </is>
+      </c>
+      <c r="C319" s="20" t="inlineStr">
+        <is>
+          <t>DRMF: Degradation-Robust Multi-Modal Image Fusion via Composable Diffusion Prior</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="n">
+        <v>108</v>
+      </c>
+      <c r="E319" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="320" ht="42" customHeight="1">
+      <c r="A320" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B320" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:ye4kPcJQO24C</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="inlineStr">
+        <is>
+          <t>DSPFusion: Image fusion via degradation and semantic dual-prior guidance</t>
+        </is>
+      </c>
+      <c r="D320" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E320" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="321" ht="42" customHeight="1">
+      <c r="A321" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B321" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:j8SEvjWlNXcC</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr">
+        <is>
+          <t>From single-modal to multi-modal: A survey and perspective on adversarial attacks in multi-modal visual systems</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="322" ht="42" customHeight="1">
+      <c r="A322" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B322" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:fEOibwPWpKIC</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="inlineStr">
+        <is>
+          <t>GText-IF: Leveraging Text-Driven Semantics for Degradation-Aware Image Fusion</t>
+        </is>
+      </c>
+      <c r="D322" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="323" ht="42" customHeight="1">
+      <c r="A323" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B323" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:7T2F9Uy0os0C</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>GTMFuse: Group-attention transformer-driven multiscale dense feature-enhanced network for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E323" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="324" ht="42" customHeight="1">
+      <c r="A324" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B324" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:_Re3VWB3Y0AC</t>
+        </is>
+      </c>
+      <c r="C324" s="20" t="inlineStr">
+        <is>
+          <t>Human-machine collaboration in reshaping visual perception and cognition</t>
+        </is>
+      </c>
+      <c r="D324" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="325" ht="42" customHeight="1">
+      <c r="A325" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B325" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:5Ul4iDaHHb8C</t>
+        </is>
+      </c>
+      <c r="C325" s="20" t="inlineStr">
+        <is>
+          <t>Image fusion in the loop of high-level vision tasks: A semantic-aware real-time infrared and visible image fusion network</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E325" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F325" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="326" ht="42" customHeight="1">
+      <c r="A326" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B326" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:BrmTIyaxlBUC</t>
+        </is>
+      </c>
+      <c r="C326" s="20" t="inlineStr">
+        <is>
+          <t>Infrared and visible image fusion via parallel scene and texture learning</t>
+        </is>
+      </c>
+      <c r="D326" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E326" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="327" ht="42" customHeight="1">
+      <c r="A327" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B327" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:uLbwQdceFCQC</t>
+        </is>
+      </c>
+      <c r="C327" s="20" t="inlineStr">
+        <is>
+          <t>Mask-DiFuser: A masked diffusion model for unified unsupervised image fusion</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="E327" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B328" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:VOx2b1Wkg3QC</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="inlineStr">
+        <is>
+          <t>PIAFusion: A progressive infrared and visible image fusion network based on illumination aware</t>
+        </is>
+      </c>
+      <c r="D328" s="16" t="n">
+        <v>1484</v>
+      </c>
+      <c r="E328" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F328" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="329" ht="42" customHeight="1">
+      <c r="A329" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B329" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Mojj43d5GZwC</t>
+        </is>
+      </c>
+      <c r="C329" s="20" t="inlineStr">
+        <is>
+          <t>PTET: A progressive token exchanging transformer for infrared and visible image fusion</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E329" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="330" ht="42" customHeight="1">
+      <c r="A330" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B330" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:2KloaMYe4IUC</t>
+        </is>
+      </c>
+      <c r="C330" s="20" t="inlineStr">
+        <is>
+          <t>ReCoFuse: Ultra-Robust Image Fusion via Restorative Multi-Modal Diffusion Reciprocal Coupling</t>
+        </is>
+      </c>
+      <c r="D330" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E330" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="331" ht="42" customHeight="1">
+      <c r="A331" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B331" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:XiVPGOgt02cC</t>
+        </is>
+      </c>
+      <c r="C331" s="20" t="inlineStr">
+        <is>
+          <t>Rethinking the necessity of image fusion in high-level vision tasks: A practical infrared and visible image fusion network based on progressive semantic injection and scene …</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="n">
+        <v>484</v>
+      </c>
+      <c r="E331" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F331" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="332" ht="42" customHeight="1">
+      <c r="A332" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B332" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:geHnlv5EZngC</t>
+        </is>
+      </c>
+      <c r="C332" s="20" t="inlineStr">
+        <is>
+          <t>STDFusionNet: An infrared and visible image fusion network based on salient target detection</t>
+        </is>
+      </c>
+      <c r="D332" s="16" t="n">
+        <v>729</v>
+      </c>
+      <c r="E332" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F332" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B333" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:wbdj-CoPYUoC</t>
+        </is>
+      </c>
+      <c r="C333" s="20" t="inlineStr">
+        <is>
+          <t>SuperFusion: A versatile image registration and fusion network with semantic awareness</t>
+        </is>
+      </c>
+      <c r="D333" s="16" t="n">
+        <v>576</v>
+      </c>
+      <c r="E333" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F333" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="334" ht="42" customHeight="1">
+      <c r="A334" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B334" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:tzM49s52ZIMC</t>
+        </is>
+      </c>
+      <c r="C334" s="20" t="inlineStr">
+        <is>
+          <t>Supplementary Material of “VideoFusion: A Spatio-Temporal Collaborative Network for Multi-modal Video Fusion”</t>
+        </is>
+      </c>
+      <c r="D334" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="335" ht="42" customHeight="1">
+      <c r="A335" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B335" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:eJXPG6dFmWUC</t>
+        </is>
+      </c>
+      <c r="C335" s="20" t="inlineStr">
+        <is>
+          <t>SwinFusion: Cross-domain long-range learning for general image fusion via swin transformer</t>
+        </is>
+      </c>
+      <c r="D335" s="16" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E335" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F335" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="336" ht="42" customHeight="1">
+      <c r="A336" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B336" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:JQOojiI6XY0C</t>
+        </is>
+      </c>
+      <c r="C336" s="20" t="inlineStr">
+        <is>
+          <t>Temcoco: Temporally consistent multi-modal video fusion with visual-semantic collaboration</t>
+        </is>
+      </c>
+      <c r="D336" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E336" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F336" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="337" ht="42" customHeight="1">
+      <c r="A337" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B337" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:Y5dfb0dijaUC</t>
+        </is>
+      </c>
+      <c r="C337" s="20" t="inlineStr">
+        <is>
+          <t>Text-if: Leveraging semantic text guidance for degradation-aware and interactive image fusion</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="n">
+        <v>397</v>
+      </c>
+      <c r="E337" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F337" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="338" ht="42" customHeight="1">
+      <c r="A338" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B338" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:evX43VCCuoAC</t>
+        </is>
+      </c>
+      <c r="C338" s="20" t="inlineStr">
+        <is>
+          <t>Videofusion: a spatio-temporal collaborative network for multi-modal video fusion</t>
+        </is>
+      </c>
+      <c r="D338" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E338" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F338" s="17" t="n">
+        <v>46322.62367584182</v>
+      </c>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="18" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B339" s="19" t="inlineStr">
+        <is>
+          <t>PyRqpAsAAAAJ:NJ774b8OgUMC</t>
+        </is>
+      </c>
+      <c r="C339" s="20" t="inlineStr">
+        <is>
+          <t>基于深度学习的图像融合方法综述</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E339" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" s="17" t="n">
+        <v>46322.62367584182</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F301"/>
+  <autoFilter ref="A1:F339"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>